--- a/data/numeric/input/data_144/1.xlsx
+++ b/data/numeric/input/data_144/1.xlsx
@@ -8438,13 +8438,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EAB10EB-80A1-43FD-BD09-3DA5108DEAB3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFDE682D-86B3-4366-A1DD-FD572C48D397}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0B7E20E-AA43-4DFF-8225-3D050A2130FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F73B4F4-630E-4E05-AD5E-20A620213A9C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76A658E4-A10E-44E0-9F13-CB632D5CD8BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07FB6CEC-B01A-4E5D-8611-EF3B5C1BA2AB}"/>
 </file>